--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M423"/>
+  <dimension ref="A1:M424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19469,6 +19469,51 @@
         <v>324.47</v>
       </c>
       <c r="M423" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>319.94</v>
+      </c>
+      <c r="C424" t="n">
+        <v>313.59</v>
+      </c>
+      <c r="D424" t="n">
+        <v>316.79</v>
+      </c>
+      <c r="E424" t="n">
+        <v>326.48</v>
+      </c>
+      <c r="F424" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="G424" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="H424" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="I424" t="n">
+        <v>328.39</v>
+      </c>
+      <c r="J424" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="K424" t="n">
+        <v>319.42</v>
+      </c>
+      <c r="L424" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="M424" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19485,7 +19530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23758,6 +23803,16 @@
       </c>
       <c r="B427" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -23926,28 +23981,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5345053875955285</v>
+        <v>-0.5308146711633694</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1898648885923268</v>
+        <v>0.1880954800754623</v>
       </c>
       <c r="M2" t="n">
-        <v>6.813841782981157</v>
+        <v>6.816494790870803</v>
       </c>
       <c r="N2" t="n">
-        <v>67.59244666472134</v>
+        <v>67.59350073270767</v>
       </c>
       <c r="O2" t="n">
-        <v>8.221462562386412</v>
+        <v>8.221526666788089</v>
       </c>
       <c r="P2" t="n">
-        <v>325.7617174622824</v>
+        <v>325.7226438320309</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24008,28 +24063,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4694029105361722</v>
+        <v>-0.4662554238115424</v>
       </c>
       <c r="J3" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.203631584622424</v>
+        <v>0.2018195122408007</v>
       </c>
       <c r="M3" t="n">
-        <v>5.552534005671327</v>
+        <v>5.555718678112521</v>
       </c>
       <c r="N3" t="n">
-        <v>47.77950424558217</v>
+        <v>47.78353249989104</v>
       </c>
       <c r="O3" t="n">
-        <v>6.912272003153679</v>
+        <v>6.912563381256699</v>
       </c>
       <c r="P3" t="n">
-        <v>318.9132826138125</v>
+        <v>318.879960158739</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24090,28 +24145,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5066694009918209</v>
+        <v>-0.5041704709932793</v>
       </c>
       <c r="J4" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3046697610687878</v>
+        <v>0.3030904788761558</v>
       </c>
       <c r="M4" t="n">
-        <v>4.523713391553787</v>
+        <v>4.52668460538708</v>
       </c>
       <c r="N4" t="n">
-        <v>32.48570642729585</v>
+        <v>32.48264753867142</v>
       </c>
       <c r="O4" t="n">
-        <v>5.699623358371661</v>
+        <v>5.699355010759676</v>
       </c>
       <c r="P4" t="n">
-        <v>324.5466500373001</v>
+        <v>324.520193854989</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24172,28 +24227,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4781119176934483</v>
+        <v>-0.4763347719039424</v>
       </c>
       <c r="J5" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4483755346157852</v>
+        <v>0.4471028875905693</v>
       </c>
       <c r="M5" t="n">
-        <v>3.101525837130991</v>
+        <v>3.104874593243791</v>
       </c>
       <c r="N5" t="n">
-        <v>15.59344049438328</v>
+        <v>15.59387048197685</v>
       </c>
       <c r="O5" t="n">
-        <v>3.948853060621943</v>
+        <v>3.948907504864712</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1054128958621</v>
+        <v>335.0865982459808</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24254,28 +24309,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4676765379854688</v>
+        <v>-0.4669887570749983</v>
       </c>
       <c r="J6" t="n">
+        <v>423</v>
+      </c>
+      <c r="K6" t="n">
         <v>422</v>
       </c>
-      <c r="K6" t="n">
-        <v>421</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.5953101691643328</v>
+        <v>0.5955733937698779</v>
       </c>
       <c r="M6" t="n">
-        <v>2.213050006196286</v>
+        <v>2.211350125273236</v>
       </c>
       <c r="N6" t="n">
-        <v>8.17473875254491</v>
+        <v>8.160886012020072</v>
       </c>
       <c r="O6" t="n">
-        <v>2.859150005254168</v>
+        <v>2.85672645033088</v>
       </c>
       <c r="P6" t="n">
-        <v>338.8496047323443</v>
+        <v>338.8422796250736</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24336,28 +24391,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4066415204645119</v>
+        <v>-0.406278017344224</v>
       </c>
       <c r="J7" t="n">
+        <v>423</v>
+      </c>
+      <c r="K7" t="n">
         <v>422</v>
       </c>
-      <c r="K7" t="n">
-        <v>421</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5241757980720352</v>
+        <v>0.52485834359149</v>
       </c>
       <c r="M7" t="n">
-        <v>2.12107557368284</v>
+        <v>2.11757924831883</v>
       </c>
       <c r="N7" t="n">
-        <v>8.252712766946692</v>
+        <v>8.234698102538678</v>
       </c>
       <c r="O7" t="n">
-        <v>2.872753516566761</v>
+        <v>2.869616368530588</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0001216779731</v>
+        <v>341.9962502425947</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24418,28 +24473,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3352336060068468</v>
+        <v>-0.3346347289683507</v>
       </c>
       <c r="J8" t="n">
+        <v>423</v>
+      </c>
+      <c r="K8" t="n">
         <v>422</v>
       </c>
-      <c r="K8" t="n">
-        <v>421</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.4516757169834447</v>
+        <v>0.4518187531590053</v>
       </c>
       <c r="M8" t="n">
-        <v>2.058140945703866</v>
+        <v>2.056546098327473</v>
       </c>
       <c r="N8" t="n">
-        <v>7.500834101223931</v>
+        <v>7.487243790999116</v>
       </c>
       <c r="O8" t="n">
-        <v>2.738765068643882</v>
+        <v>2.736282841922435</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7769174385655</v>
+        <v>342.7705391886284</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24500,28 +24555,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3036183587829203</v>
+        <v>-0.3027212181323985</v>
       </c>
       <c r="J9" t="n">
+        <v>423</v>
+      </c>
+      <c r="K9" t="n">
         <v>422</v>
       </c>
-      <c r="K9" t="n">
-        <v>421</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3838985796190175</v>
+        <v>0.3833400048450778</v>
       </c>
       <c r="M9" t="n">
-        <v>2.193097193403245</v>
+        <v>2.192872144668268</v>
       </c>
       <c r="N9" t="n">
-        <v>8.133837420377159</v>
+        <v>8.123952714903551</v>
       </c>
       <c r="O9" t="n">
-        <v>2.851988327531717</v>
+        <v>2.850254850869225</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4040481572785</v>
+        <v>334.3944932955457</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24582,28 +24637,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2538506822502317</v>
+        <v>-0.253994602964046</v>
       </c>
       <c r="J10" t="n">
+        <v>423</v>
+      </c>
+      <c r="K10" t="n">
         <v>422</v>
       </c>
-      <c r="K10" t="n">
-        <v>421</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2474097168374422</v>
+        <v>0.2484956758979511</v>
       </c>
       <c r="M10" t="n">
-        <v>2.561824535722481</v>
+        <v>2.556654768654092</v>
       </c>
       <c r="N10" t="n">
-        <v>10.77710838208472</v>
+        <v>10.75181185758853</v>
       </c>
       <c r="O10" t="n">
-        <v>3.282850648763163</v>
+        <v>3.278995556201401</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7357595381883</v>
+        <v>328.7372923441314</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24664,28 +24719,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2375908638104246</v>
+        <v>-0.2383047352984051</v>
       </c>
       <c r="J11" t="n">
+        <v>423</v>
+      </c>
+      <c r="K11" t="n">
         <v>422</v>
       </c>
-      <c r="K11" t="n">
-        <v>421</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1837049047934914</v>
+        <v>0.1852516046855115</v>
       </c>
       <c r="M11" t="n">
-        <v>2.938803767290945</v>
+        <v>2.935773205133611</v>
       </c>
       <c r="N11" t="n">
-        <v>13.7908055255556</v>
+        <v>13.76407120726733</v>
       </c>
       <c r="O11" t="n">
-        <v>3.713597383340795</v>
+        <v>3.709996119575778</v>
       </c>
       <c r="P11" t="n">
-        <v>327.2790829044671</v>
+        <v>327.2866858855144</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24746,28 +24801,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.227544293103474</v>
+        <v>-0.2279498487108432</v>
       </c>
       <c r="J12" t="n">
+        <v>423</v>
+      </c>
+      <c r="K12" t="n">
         <v>422</v>
       </c>
-      <c r="K12" t="n">
-        <v>421</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2496645143854173</v>
+        <v>0.2511754384466203</v>
       </c>
       <c r="M12" t="n">
-        <v>2.313193273078082</v>
+        <v>2.310099791581291</v>
       </c>
       <c r="N12" t="n">
-        <v>8.555281192444376</v>
+        <v>8.536926840577694</v>
       </c>
       <c r="O12" t="n">
-        <v>2.924941228887236</v>
+        <v>2.921801985175877</v>
       </c>
       <c r="P12" t="n">
-        <v>332.1996173244899</v>
+        <v>332.2039366335649</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24809,7 +24864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M423"/>
+  <dimension ref="A1:M424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53125,6 +53180,73 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-42.82760696344651,173.33511458170722</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-42.82803252598229,173.33442427050852</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-42.828522719155835,173.33381131487076</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-42.82907302835214,173.333283245363</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-42.82958708412983,173.3327118639006</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-42.830117732074605,173.33217334870594</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-42.83065459289269,173.3316307276947</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-42.83120110242118,173.3311014919157</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-42.831749192386404,173.33059280349593</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-42.832315072811184,173.33013191201508</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-42.83291651997928,173.32975866291494</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M424"/>
+  <dimension ref="A1:M426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19516,6 +19516,96 @@
       <c r="M424" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="C425" t="n">
+        <v>313.47</v>
+      </c>
+      <c r="D425" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="E425" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="F425" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="G425" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="H425" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="I425" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="J425" t="n">
+        <v>322.07</v>
+      </c>
+      <c r="K425" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="L425" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>319.61</v>
+      </c>
+      <c r="C426" t="n">
+        <v>313.46</v>
+      </c>
+      <c r="D426" t="n">
+        <v>315.77</v>
+      </c>
+      <c r="E426" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="F426" t="n">
+        <v>327.27</v>
+      </c>
+      <c r="G426" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="H426" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="I426" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="J426" t="n">
+        <v>322.09</v>
+      </c>
+      <c r="K426" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="L426" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19530,7 +19620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B428"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23813,6 +23903,26 @@
       </c>
       <c r="B428" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -23981,28 +24091,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5308146711633694</v>
+        <v>-0.5237454926503643</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1880954800754623</v>
+        <v>0.1847926426323898</v>
       </c>
       <c r="M2" t="n">
-        <v>6.816494790870803</v>
+        <v>6.82008849892209</v>
       </c>
       <c r="N2" t="n">
-        <v>67.59350073270767</v>
+        <v>67.57042515923828</v>
       </c>
       <c r="O2" t="n">
-        <v>8.221526666788089</v>
+        <v>8.220123183945498</v>
       </c>
       <c r="P2" t="n">
-        <v>325.7226438320309</v>
+        <v>325.6474920079806</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24063,28 +24173,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4662554238115424</v>
+        <v>-0.4601190900696941</v>
       </c>
       <c r="J3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2018195122408007</v>
+        <v>0.1983393633048339</v>
       </c>
       <c r="M3" t="n">
-        <v>5.555718678112521</v>
+        <v>5.560977278189131</v>
       </c>
       <c r="N3" t="n">
-        <v>47.78353249989104</v>
+        <v>47.78095098520092</v>
       </c>
       <c r="O3" t="n">
-        <v>6.912563381256699</v>
+        <v>6.912376652440239</v>
       </c>
       <c r="P3" t="n">
-        <v>318.879960158739</v>
+        <v>318.81472501874</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24145,28 +24255,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5041704709932793</v>
+        <v>-0.5000693652530637</v>
       </c>
       <c r="J4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3030904788761558</v>
+        <v>0.3009850711551214</v>
       </c>
       <c r="M4" t="n">
-        <v>4.52668460538708</v>
+        <v>4.527674199817008</v>
       </c>
       <c r="N4" t="n">
-        <v>32.48264753867142</v>
+        <v>32.42908060751973</v>
       </c>
       <c r="O4" t="n">
-        <v>5.699355010759676</v>
+        <v>5.694653686355275</v>
       </c>
       <c r="P4" t="n">
-        <v>324.520193854989</v>
+        <v>324.4765954574152</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24227,28 +24337,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4763347719039424</v>
+        <v>-0.4739986149684148</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4471028875905693</v>
+        <v>0.4464839103406075</v>
       </c>
       <c r="M5" t="n">
-        <v>3.104874593243791</v>
+        <v>3.104267308167789</v>
       </c>
       <c r="N5" t="n">
-        <v>15.59387048197685</v>
+        <v>15.5528943521023</v>
       </c>
       <c r="O5" t="n">
-        <v>3.948907504864712</v>
+        <v>3.943715805189606</v>
       </c>
       <c r="P5" t="n">
-        <v>335.0865982459808</v>
+        <v>335.0617645786468</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24309,28 +24419,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4669887570749983</v>
+        <v>-0.4663442009352179</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5955733937698779</v>
+        <v>0.5971104536781228</v>
       </c>
       <c r="M6" t="n">
-        <v>2.211350125273236</v>
+        <v>2.20419486503106</v>
       </c>
       <c r="N6" t="n">
-        <v>8.160886012020072</v>
+        <v>8.124839490286178</v>
       </c>
       <c r="O6" t="n">
-        <v>2.85672645033088</v>
+        <v>2.850410407342455</v>
       </c>
       <c r="P6" t="n">
-        <v>338.8422796250736</v>
+        <v>338.8353858484462</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24391,28 +24501,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.406278017344224</v>
+        <v>-0.406058602124202</v>
       </c>
       <c r="J7" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L7" t="n">
-        <v>0.52485834359149</v>
+        <v>0.5269326557952159</v>
       </c>
       <c r="M7" t="n">
-        <v>2.11757924831883</v>
+        <v>2.108499895663688</v>
       </c>
       <c r="N7" t="n">
-        <v>8.234698102538678</v>
+        <v>8.196257430978555</v>
       </c>
       <c r="O7" t="n">
-        <v>2.869616368530588</v>
+        <v>2.86291065717716</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9962502425947</v>
+        <v>341.9939021759501</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24473,28 +24583,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3346347289683507</v>
+        <v>-0.3335552741740472</v>
       </c>
       <c r="J8" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K8" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4518187531590053</v>
+        <v>0.4523259250449538</v>
       </c>
       <c r="M8" t="n">
-        <v>2.056546098327473</v>
+        <v>2.052749746537099</v>
       </c>
       <c r="N8" t="n">
-        <v>7.487243790999116</v>
+        <v>7.458931725133678</v>
       </c>
       <c r="O8" t="n">
-        <v>2.736282841922435</v>
+        <v>2.731104488139126</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7705391886284</v>
+        <v>342.7589931340841</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24555,28 +24665,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3027212181323985</v>
+        <v>-0.3015563648843682</v>
       </c>
       <c r="J9" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K9" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3833400048450778</v>
+        <v>0.3835187715380884</v>
       </c>
       <c r="M9" t="n">
-        <v>2.192872144668268</v>
+        <v>2.188998539754523</v>
       </c>
       <c r="N9" t="n">
-        <v>8.123952714903551</v>
+        <v>8.093577594965684</v>
       </c>
       <c r="O9" t="n">
-        <v>2.850254850869225</v>
+        <v>2.844921368854627</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3944932955457</v>
+        <v>334.3820352334143</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24637,28 +24747,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.253994602964046</v>
+        <v>-0.2539398306576754</v>
       </c>
       <c r="J10" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K10" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2484956758979511</v>
+        <v>0.2501831881435317</v>
       </c>
       <c r="M10" t="n">
-        <v>2.556654768654092</v>
+        <v>2.544826854805295</v>
       </c>
       <c r="N10" t="n">
-        <v>10.75181185758853</v>
+        <v>10.7011143952932</v>
       </c>
       <c r="O10" t="n">
-        <v>3.278995556201401</v>
+        <v>3.271255782615172</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7372923441314</v>
+        <v>328.7367064415688</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24719,28 +24829,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2383047352984051</v>
+        <v>-0.2401009143488741</v>
       </c>
       <c r="J11" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K11" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1852516046855115</v>
+        <v>0.1887610657250858</v>
       </c>
       <c r="M11" t="n">
-        <v>2.935773205133611</v>
+        <v>2.931692876738061</v>
       </c>
       <c r="N11" t="n">
-        <v>13.76407120726733</v>
+        <v>13.71811051842309</v>
       </c>
       <c r="O11" t="n">
-        <v>3.709996119575778</v>
+        <v>3.703796770669672</v>
       </c>
       <c r="P11" t="n">
-        <v>327.2866858855144</v>
+        <v>327.3058929571122</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24801,28 +24911,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2279498487108432</v>
+        <v>-0.2282875271836024</v>
       </c>
       <c r="J12" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K12" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2511754384466203</v>
+        <v>0.2534927545353236</v>
       </c>
       <c r="M12" t="n">
-        <v>2.310099791581291</v>
+        <v>2.301170022983813</v>
       </c>
       <c r="N12" t="n">
-        <v>8.536926840577694</v>
+        <v>8.497734316510728</v>
       </c>
       <c r="O12" t="n">
-        <v>2.921801985175877</v>
+        <v>2.915087360013543</v>
       </c>
       <c r="P12" t="n">
-        <v>332.2039366335649</v>
+        <v>332.2075449480085</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24864,7 +24974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M424"/>
+  <dimension ref="A1:M426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53247,6 +53357,140 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-42.827605376727284,173.33511241189936</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-42.82803176435272,173.33442322899944</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-42.828516882412,173.3338029854023</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-42.829066135489626,173.33327258131996</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-42.829581826289846,173.33270332399235</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-42.83011346239438,173.33216623875703</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-42.83065281526223,173.3316271915035</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-42.831197658106646,173.33109317462632</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-42.83175071440687,173.33059655343564</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-42.83231237664224,173.33012526921814</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-42.83291738971531,173.3297608057704</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-42.82760486897711,173.3351117175609</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-42.828031700883585,173.33442314220702</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-42.82851638566782,173.3338022765114</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-42.82906369921901,173.3332688121329</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-42.82958257740988,173.33270454397916</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-42.83011517026653,173.33216908273647</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-42.83065489762932,173.3316313338989</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-42.83119836463275,173.33109488073688</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-42.83175080137946,173.3305967677179</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-42.83231385518654,173.3301289120422</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-42.832919911949546,173.3297670200516</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M426"/>
+  <dimension ref="A1:M427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19606,6 +19606,51 @@
       <c r="M426" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="C427" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="D427" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="E427" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="F427" t="n">
+        <v>327.26</v>
+      </c>
+      <c r="G427" t="n">
+        <v>330.88</v>
+      </c>
+      <c r="H427" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="I427" t="n">
+        <v>328.11</v>
+      </c>
+      <c r="J427" t="n">
+        <v>322.09</v>
+      </c>
+      <c r="K427" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="L427" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23923,6 +23968,16 @@
       </c>
       <c r="B430" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -24091,28 +24146,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5237454926503643</v>
+        <v>-0.5198362441487365</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1847926426323898</v>
+        <v>0.1828597157809527</v>
       </c>
       <c r="M2" t="n">
-        <v>6.82008849892209</v>
+        <v>6.823595080557493</v>
       </c>
       <c r="N2" t="n">
-        <v>67.57042515923828</v>
+        <v>67.59116856559223</v>
       </c>
       <c r="O2" t="n">
-        <v>8.220123183945498</v>
+        <v>8.221384832593122</v>
       </c>
       <c r="P2" t="n">
-        <v>325.6474920079806</v>
+        <v>325.6056769353123</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24173,28 +24228,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4601190900696941</v>
+        <v>-0.4566810567267436</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1983393633048339</v>
+        <v>0.1962570482558683</v>
       </c>
       <c r="M3" t="n">
-        <v>5.560977278189131</v>
+        <v>5.565337360748539</v>
       </c>
       <c r="N3" t="n">
-        <v>47.78095098520092</v>
+        <v>47.80751511487939</v>
       </c>
       <c r="O3" t="n">
-        <v>6.912376652440239</v>
+        <v>6.914297875770134</v>
       </c>
       <c r="P3" t="n">
-        <v>318.81472501874</v>
+        <v>318.7779502744352</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24255,28 +24310,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5000693652530637</v>
+        <v>-0.4978198914645591</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3009850711551214</v>
+        <v>0.2997046855055423</v>
       </c>
       <c r="M4" t="n">
-        <v>4.527674199817008</v>
+        <v>4.529124013364799</v>
       </c>
       <c r="N4" t="n">
-        <v>32.42908060751973</v>
+        <v>32.41234411828324</v>
       </c>
       <c r="O4" t="n">
-        <v>5.694653686355275</v>
+        <v>5.693184005306981</v>
       </c>
       <c r="P4" t="n">
-        <v>324.4765954574152</v>
+        <v>324.4525340783823</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24337,28 +24392,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4739986149684148</v>
+        <v>-0.4727136030876579</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4464839103406075</v>
+        <v>0.4460095129579664</v>
       </c>
       <c r="M5" t="n">
-        <v>3.104267308167789</v>
+        <v>3.104646722896307</v>
       </c>
       <c r="N5" t="n">
-        <v>15.5528943521023</v>
+        <v>15.5357651286101</v>
       </c>
       <c r="O5" t="n">
-        <v>3.943715805189606</v>
+        <v>3.941543495714604</v>
       </c>
       <c r="P5" t="n">
-        <v>335.0617645786468</v>
+        <v>335.048019516098</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24419,28 +24474,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4663442009352179</v>
+        <v>-0.4659743857570595</v>
       </c>
       <c r="J6" t="n">
+        <v>426</v>
+      </c>
+      <c r="K6" t="n">
         <v>425</v>
       </c>
-      <c r="K6" t="n">
-        <v>424</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.5971104536781228</v>
+        <v>0.5978303158884033</v>
       </c>
       <c r="M6" t="n">
-        <v>2.20419486503106</v>
+        <v>2.200858787362066</v>
       </c>
       <c r="N6" t="n">
-        <v>8.124839490286178</v>
+        <v>8.107307983144661</v>
       </c>
       <c r="O6" t="n">
-        <v>2.850410407342455</v>
+        <v>2.847333486464952</v>
       </c>
       <c r="P6" t="n">
-        <v>338.8353858484462</v>
+        <v>338.8314067663329</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24501,28 +24556,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.406058602124202</v>
+        <v>-0.4062030497235649</v>
       </c>
       <c r="J7" t="n">
+        <v>426</v>
+      </c>
+      <c r="K7" t="n">
         <v>425</v>
       </c>
-      <c r="K7" t="n">
-        <v>424</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5269326557952159</v>
+        <v>0.5282927962143401</v>
       </c>
       <c r="M7" t="n">
-        <v>2.108499895663688</v>
+        <v>2.104452547935755</v>
       </c>
       <c r="N7" t="n">
-        <v>8.196257430978555</v>
+        <v>8.177214049121341</v>
       </c>
       <c r="O7" t="n">
-        <v>2.86291065717716</v>
+        <v>2.859582845297779</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9939021759501</v>
+        <v>341.9954563816531</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24583,28 +24638,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3335552741740472</v>
+        <v>-0.3330812304613648</v>
       </c>
       <c r="J8" t="n">
+        <v>426</v>
+      </c>
+      <c r="K8" t="n">
         <v>425</v>
       </c>
-      <c r="K8" t="n">
-        <v>424</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.4523259250449538</v>
+        <v>0.4527176065541559</v>
       </c>
       <c r="M8" t="n">
-        <v>2.052749746537099</v>
+        <v>2.050479461331822</v>
       </c>
       <c r="N8" t="n">
-        <v>7.458931725133678</v>
+        <v>7.443986883427556</v>
       </c>
       <c r="O8" t="n">
-        <v>2.731104488139126</v>
+        <v>2.728367072706229</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7589931340841</v>
+        <v>342.7538925893541</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24665,28 +24720,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3015563648843682</v>
+        <v>-0.3007743469510064</v>
       </c>
       <c r="J9" t="n">
+        <v>426</v>
+      </c>
+      <c r="K9" t="n">
         <v>425</v>
       </c>
-      <c r="K9" t="n">
-        <v>424</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3835187715380884</v>
+        <v>0.3832124917545231</v>
       </c>
       <c r="M9" t="n">
-        <v>2.188998539754523</v>
+        <v>2.188165038550849</v>
       </c>
       <c r="N9" t="n">
-        <v>8.093577594965684</v>
+        <v>8.081624793999037</v>
       </c>
       <c r="O9" t="n">
-        <v>2.844921368854627</v>
+        <v>2.84281986661115</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3820352334143</v>
+        <v>334.3736209936678</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24747,28 +24802,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2539398306576754</v>
+        <v>-0.2538935719557395</v>
       </c>
       <c r="J10" t="n">
+        <v>426</v>
+      </c>
+      <c r="K10" t="n">
         <v>425</v>
       </c>
-      <c r="K10" t="n">
-        <v>424</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2501831881435317</v>
+        <v>0.2510111475750749</v>
       </c>
       <c r="M10" t="n">
-        <v>2.544826854805295</v>
+        <v>2.539031756384329</v>
       </c>
       <c r="N10" t="n">
-        <v>10.7011143952932</v>
+        <v>10.67596011423973</v>
       </c>
       <c r="O10" t="n">
-        <v>3.271255782615172</v>
+        <v>3.267408776728086</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7367064415688</v>
+        <v>328.7362087140976</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24829,28 +24884,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2401009143488741</v>
+        <v>-0.2411362865708875</v>
       </c>
       <c r="J11" t="n">
+        <v>426</v>
+      </c>
+      <c r="K11" t="n">
         <v>425</v>
       </c>
-      <c r="K11" t="n">
-        <v>424</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1887610657250858</v>
+        <v>0.1906785695047311</v>
       </c>
       <c r="M11" t="n">
-        <v>2.931692876738061</v>
+        <v>2.930355049253089</v>
       </c>
       <c r="N11" t="n">
-        <v>13.71811051842309</v>
+        <v>13.69826233943474</v>
       </c>
       <c r="O11" t="n">
-        <v>3.703796770669672</v>
+        <v>3.70111636394139</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3058929571122</v>
+        <v>327.3170332004893</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24911,28 +24966,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2282875271836024</v>
+        <v>-0.2283357262002469</v>
       </c>
       <c r="J12" t="n">
+        <v>426</v>
+      </c>
+      <c r="K12" t="n">
         <v>425</v>
       </c>
-      <c r="K12" t="n">
-        <v>424</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2534927545353236</v>
+        <v>0.2544769902516038</v>
       </c>
       <c r="M12" t="n">
-        <v>2.301170022983813</v>
+        <v>2.29603200516122</v>
       </c>
       <c r="N12" t="n">
-        <v>8.497734316510728</v>
+        <v>8.477766584266501</v>
       </c>
       <c r="O12" t="n">
-        <v>2.915087360013543</v>
+        <v>2.911660451403374</v>
       </c>
       <c r="P12" t="n">
-        <v>332.2075449480085</v>
+        <v>332.2080635525882</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24974,7 +25029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M426"/>
+  <dimension ref="A1:M427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53491,6 +53546,73 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-42.827610454228676,173.33511935528486</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-42.828037032290375,173.334430432771</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-42.82851924194682,173.333806352634</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-42.8290662543321,173.33327276518273</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-42.82958251963142,173.33270445013403</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-42.83011084365694,173.33216187798885</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-42.83065296763057,173.33162749460558</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-42.83119986600065,173.33109850622196</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-42.83175080137946,173.3305967677179</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-42.83231159388344,173.3301233406643</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-42.83291969451559,173.32976648433768</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M427"/>
+  <dimension ref="A1:M429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19649,6 +19649,96 @@
         <v>326.03</v>
       </c>
       <c r="M427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="C428" t="n">
+        <v>313.77</v>
+      </c>
+      <c r="D428" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="E428" t="n">
+        <v>325.92</v>
+      </c>
+      <c r="F428" t="n">
+        <v>327.87</v>
+      </c>
+      <c r="G428" t="n">
+        <v>330.65</v>
+      </c>
+      <c r="H428" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="I428" t="n">
+        <v>328.02</v>
+      </c>
+      <c r="J428" t="n">
+        <v>322.04</v>
+      </c>
+      <c r="K428" t="n">
+        <v>318.15</v>
+      </c>
+      <c r="L428" t="n">
+        <v>326.21</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="C429" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="D429" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="E429" t="n">
+        <v>326.11</v>
+      </c>
+      <c r="F429" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="G429" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="H429" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="I429" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="J429" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="K429" t="n">
+        <v>319.52</v>
+      </c>
+      <c r="L429" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="M429" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19665,7 +19755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23978,6 +24068,26 @@
       </c>
       <c r="B431" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -24146,28 +24256,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5198362441487365</v>
+        <v>-0.5121525657425552</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1828597157809527</v>
+        <v>0.1790884115961936</v>
       </c>
       <c r="M2" t="n">
-        <v>6.823595080557493</v>
+        <v>6.829643955611767</v>
       </c>
       <c r="N2" t="n">
-        <v>67.59116856559223</v>
+        <v>67.62335583645503</v>
       </c>
       <c r="O2" t="n">
-        <v>8.221384832593122</v>
+        <v>8.223342133004989</v>
       </c>
       <c r="P2" t="n">
-        <v>325.6056769353123</v>
+        <v>325.523241337207</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24228,28 +24338,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4566810567267436</v>
+        <v>-0.450443775344911</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1962570482558683</v>
+        <v>0.1926833166894379</v>
       </c>
       <c r="M3" t="n">
-        <v>5.565337360748539</v>
+        <v>5.571081221153838</v>
       </c>
       <c r="N3" t="n">
-        <v>47.80751511487939</v>
+        <v>47.81345261397131</v>
       </c>
       <c r="O3" t="n">
-        <v>6.914297875770134</v>
+        <v>6.914727226288201</v>
       </c>
       <c r="P3" t="n">
-        <v>318.7779502744352</v>
+        <v>318.7110325853354</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24310,28 +24420,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4978198914645591</v>
+        <v>-0.4932058192733621</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2997046855055423</v>
+        <v>0.2969816264345011</v>
       </c>
       <c r="M4" t="n">
-        <v>4.529124013364799</v>
+        <v>4.53258070438403</v>
       </c>
       <c r="N4" t="n">
-        <v>32.41234411828324</v>
+        <v>32.3863936330822</v>
       </c>
       <c r="O4" t="n">
-        <v>5.693184005306981</v>
+        <v>5.690904465292156</v>
       </c>
       <c r="P4" t="n">
-        <v>324.4525340783823</v>
+        <v>324.4030313282409</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24392,28 +24502,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4727136030876579</v>
+        <v>-0.4695582943413029</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4460095129579664</v>
+        <v>0.4441110585707247</v>
       </c>
       <c r="M5" t="n">
-        <v>3.104646722896307</v>
+        <v>3.108790137773445</v>
       </c>
       <c r="N5" t="n">
-        <v>15.5357651286101</v>
+        <v>15.52188964524144</v>
       </c>
       <c r="O5" t="n">
-        <v>3.941543495714604</v>
+        <v>3.939782943924886</v>
       </c>
       <c r="P5" t="n">
-        <v>335.048019516098</v>
+        <v>335.0141657363627</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24474,28 +24584,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4659743857570595</v>
+        <v>-0.4642044626082297</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5978303158884033</v>
+        <v>0.5977099847128902</v>
       </c>
       <c r="M6" t="n">
-        <v>2.200858787362066</v>
+        <v>2.199299520833644</v>
       </c>
       <c r="N6" t="n">
-        <v>8.107307983144661</v>
+        <v>8.088908676302934</v>
       </c>
       <c r="O6" t="n">
-        <v>2.847333486464952</v>
+        <v>2.84410067970579</v>
       </c>
       <c r="P6" t="n">
-        <v>338.8314067663329</v>
+        <v>338.8123005886905</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24556,28 +24666,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4062030497235649</v>
+        <v>-0.4068207575851251</v>
       </c>
       <c r="J7" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5282927962143401</v>
+        <v>0.5313528371614586</v>
       </c>
       <c r="M7" t="n">
-        <v>2.104452547935755</v>
+        <v>2.09846121372545</v>
       </c>
       <c r="N7" t="n">
-        <v>8.177214049121341</v>
+        <v>8.1412626074918</v>
       </c>
       <c r="O7" t="n">
-        <v>2.859582845297779</v>
+        <v>2.853289786806065</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9954563816531</v>
+        <v>342.0021242833988</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24638,28 +24748,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3330812304613648</v>
+        <v>-0.3324544987663839</v>
       </c>
       <c r="J8" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4527176065541559</v>
+        <v>0.4540659264530404</v>
       </c>
       <c r="M8" t="n">
-        <v>2.050479461331822</v>
+        <v>2.044224097073854</v>
       </c>
       <c r="N8" t="n">
-        <v>7.443986883427556</v>
+        <v>7.411537033240753</v>
       </c>
       <c r="O8" t="n">
-        <v>2.728367072706229</v>
+        <v>2.722413824759335</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7538925893541</v>
+        <v>342.7471305092329</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24720,28 +24830,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3007743469510064</v>
+        <v>-0.299682326690305</v>
       </c>
       <c r="J9" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K9" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3832124917545231</v>
+        <v>0.3835172700782649</v>
       </c>
       <c r="M9" t="n">
-        <v>2.188165038550849</v>
+        <v>2.183965902835475</v>
       </c>
       <c r="N9" t="n">
-        <v>8.081624793999037</v>
+        <v>8.051574581170147</v>
       </c>
       <c r="O9" t="n">
-        <v>2.84281986661115</v>
+        <v>2.837529661725168</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3736209936678</v>
+        <v>334.3618400537484</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24802,28 +24912,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2538935719557395</v>
+        <v>-0.2537480851527013</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K10" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2510111475750749</v>
+        <v>0.2525883287555369</v>
       </c>
       <c r="M10" t="n">
-        <v>2.539031756384329</v>
+        <v>2.527737702850371</v>
       </c>
       <c r="N10" t="n">
-        <v>10.67596011423973</v>
+        <v>10.62611985482493</v>
       </c>
       <c r="O10" t="n">
-        <v>3.267408776728086</v>
+        <v>3.25977297596396</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7362087140976</v>
+        <v>328.7346377151758</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24884,28 +24994,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2411362865708875</v>
+        <v>-0.2429625538676195</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K11" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1906785695047311</v>
+        <v>0.1942585544452761</v>
       </c>
       <c r="M11" t="n">
-        <v>2.930355049253089</v>
+        <v>2.926351592590507</v>
       </c>
       <c r="N11" t="n">
-        <v>13.69826233943474</v>
+        <v>13.65578924683792</v>
       </c>
       <c r="O11" t="n">
-        <v>3.70111636394139</v>
+        <v>3.695374033415011</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3170332004893</v>
+        <v>327.3367355476469</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24966,28 +25076,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2283357262002469</v>
+        <v>-0.2280115234102838</v>
       </c>
       <c r="J12" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K12" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2544769902516038</v>
+        <v>0.2557264744034518</v>
       </c>
       <c r="M12" t="n">
-        <v>2.29603200516122</v>
+        <v>2.286796539322105</v>
       </c>
       <c r="N12" t="n">
-        <v>8.477766584266501</v>
+        <v>8.439039881000877</v>
       </c>
       <c r="O12" t="n">
-        <v>2.911660451403374</v>
+        <v>2.905002561272688</v>
       </c>
       <c r="P12" t="n">
-        <v>332.2080635525882</v>
+        <v>332.20456203713</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25029,7 +25139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M427"/>
+  <dimension ref="A1:M429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53613,6 +53723,140 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-42.82761102544757,173.33512013641578</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-42.82803366842661,173.33442583277213</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-42.828520918458345,173.33380874514094</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-42.82906970076346,173.333278097204</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-42.82958604411759,173.3327101746879</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-42.83010953428816,173.3321596976049</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-42.8306519518417,173.331625473925</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-42.83119946857975,173.33109754653472</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-42.83175058394798,173.33059623201223</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-42.83230955001308,173.33011830499615</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-42.832920477277874,173.3297684129078</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-42.82760924832214,173.3351177062307</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-42.82803227210576,173.33442392333882</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-42.828519738690964,173.33380706152496</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-42.82907082976679,173.33327984390073</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-42.82959211085539,173.3327200284297</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-42.830107541770374,173.33215637962948</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-42.83065022500054,173.3316220387681</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-42.831195626843936,173.33108826955868</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-42.83175136670132,173.33059816055274</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-42.832315507677116,173.330132983434</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-42.832922869051345,173.32977430576125</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M429"/>
+  <dimension ref="A1:M432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19739,6 +19739,141 @@
         <v>326.76</v>
       </c>
       <c r="M429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="C430" t="n">
+        <v>313.09</v>
+      </c>
+      <c r="D430" t="n">
+        <v>315.71</v>
+      </c>
+      <c r="E430" t="n">
+        <v>325.07</v>
+      </c>
+      <c r="F430" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="G430" t="n">
+        <v>330.93</v>
+      </c>
+      <c r="H430" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="I430" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="J430" t="n">
+        <v>322.41</v>
+      </c>
+      <c r="K430" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="L430" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>318.69</v>
+      </c>
+      <c r="C431" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D431" t="n">
+        <v>314.32</v>
+      </c>
+      <c r="E431" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="F431" t="n">
+        <v>328.34</v>
+      </c>
+      <c r="G431" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="H431" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="I431" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="J431" t="n">
+        <v>321.92</v>
+      </c>
+      <c r="K431" t="n">
+        <v>319.93</v>
+      </c>
+      <c r="L431" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>318.21</v>
+      </c>
+      <c r="C432" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="D432" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="E432" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="F432" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="G432" t="n">
+        <v>330.45</v>
+      </c>
+      <c r="H432" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="I432" t="n">
+        <v>325.77</v>
+      </c>
+      <c r="J432" t="n">
+        <v>321.78</v>
+      </c>
+      <c r="K432" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="L432" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="M432" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19755,7 +19890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24088,6 +24223,36 @@
       </c>
       <c r="B433" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -24256,28 +24421,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5121525657425552</v>
+        <v>-0.5028685121312754</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1790884115961936</v>
+        <v>0.1750693358066119</v>
       </c>
       <c r="M2" t="n">
-        <v>6.829643955611767</v>
+        <v>6.827234826572838</v>
       </c>
       <c r="N2" t="n">
-        <v>67.62335583645503</v>
+        <v>67.4987327119279</v>
       </c>
       <c r="O2" t="n">
-        <v>8.223342133004989</v>
+        <v>8.215761237519498</v>
       </c>
       <c r="P2" t="n">
-        <v>325.523241337207</v>
+        <v>325.4232414949274</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24338,28 +24503,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.450443775344911</v>
+        <v>-0.4436312190203279</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1926833166894379</v>
+        <v>0.1895389578483997</v>
       </c>
       <c r="M3" t="n">
-        <v>5.571081221153838</v>
+        <v>5.566685150003532</v>
       </c>
       <c r="N3" t="n">
-        <v>47.81345261397131</v>
+        <v>47.67132544186317</v>
       </c>
       <c r="O3" t="n">
-        <v>6.914727226288201</v>
+        <v>6.90444244250491</v>
       </c>
       <c r="P3" t="n">
-        <v>318.7110325853354</v>
+        <v>318.6376586850571</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24420,28 +24585,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4932058192733621</v>
+        <v>-0.48893723010281</v>
       </c>
       <c r="J4" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2969816264345011</v>
+        <v>0.2957963282118395</v>
       </c>
       <c r="M4" t="n">
-        <v>4.53258070438403</v>
+        <v>4.523480509193356</v>
       </c>
       <c r="N4" t="n">
-        <v>32.3863936330822</v>
+        <v>32.23970750101076</v>
       </c>
       <c r="O4" t="n">
-        <v>5.690904465292156</v>
+        <v>5.67800206947926</v>
       </c>
       <c r="P4" t="n">
-        <v>324.4030313282409</v>
+        <v>324.3570611593308</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24502,28 +24667,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4695582943413029</v>
+        <v>-0.4669053100740676</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4441110585707247</v>
+        <v>0.4443259985736029</v>
       </c>
       <c r="M5" t="n">
-        <v>3.108790137773445</v>
+        <v>3.102610714900799</v>
       </c>
       <c r="N5" t="n">
-        <v>15.52188964524144</v>
+        <v>15.44384197557499</v>
       </c>
       <c r="O5" t="n">
-        <v>3.939782943924886</v>
+        <v>3.929865388989169</v>
       </c>
       <c r="P5" t="n">
-        <v>335.0141657363627</v>
+        <v>334.9855939916233</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24584,28 +24749,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4642044626082297</v>
+        <v>-0.4616730051087464</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5977099847128902</v>
+        <v>0.5977318559870632</v>
       </c>
       <c r="M6" t="n">
-        <v>2.199299520833644</v>
+        <v>2.196280069015198</v>
       </c>
       <c r="N6" t="n">
-        <v>8.088908676302934</v>
+        <v>8.057988850173162</v>
       </c>
       <c r="O6" t="n">
-        <v>2.84410067970579</v>
+        <v>2.838659692561467</v>
       </c>
       <c r="P6" t="n">
-        <v>338.8123005886905</v>
+        <v>338.7848746035284</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24666,28 +24831,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4068207575851251</v>
+        <v>-0.4074511558215141</v>
       </c>
       <c r="J7" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5313528371614586</v>
+        <v>0.5356010254899818</v>
       </c>
       <c r="M7" t="n">
-        <v>2.09846121372545</v>
+        <v>2.087730342367425</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1412626074918</v>
+        <v>8.08629200815354</v>
       </c>
       <c r="O7" t="n">
-        <v>2.853289786806065</v>
+        <v>2.843640625703878</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0021242833988</v>
+        <v>342.0089568841316</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24748,28 +24913,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3324544987663839</v>
+        <v>-0.3325821965354217</v>
       </c>
       <c r="J8" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4540659264530404</v>
+        <v>0.4576067646733546</v>
       </c>
       <c r="M8" t="n">
-        <v>2.044224097073854</v>
+        <v>2.035422010939206</v>
       </c>
       <c r="N8" t="n">
-        <v>7.411537033240753</v>
+        <v>7.364924226314887</v>
       </c>
       <c r="O8" t="n">
-        <v>2.722413824759335</v>
+        <v>2.713839388452251</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7471305092329</v>
+        <v>342.7485239522255</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24830,28 +24995,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.299682326690305</v>
+        <v>-0.2995221164852747</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K9" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3835172700782649</v>
+        <v>0.3865477330707593</v>
       </c>
       <c r="M9" t="n">
-        <v>2.183965902835475</v>
+        <v>2.172280500424717</v>
       </c>
       <c r="N9" t="n">
-        <v>8.051574581170147</v>
+        <v>7.998045982689492</v>
       </c>
       <c r="O9" t="n">
-        <v>2.837529661725168</v>
+        <v>2.828081678928226</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3618400537484</v>
+        <v>334.3601112231614</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24912,28 +25077,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2537480851527013</v>
+        <v>-0.253631045656875</v>
       </c>
       <c r="J10" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2525883287555369</v>
+        <v>0.2550931616363068</v>
       </c>
       <c r="M10" t="n">
-        <v>2.527737702850371</v>
+        <v>2.51146820047339</v>
       </c>
       <c r="N10" t="n">
-        <v>10.62611985482493</v>
+        <v>10.55252595380516</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25977297596396</v>
+        <v>3.248465168938273</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7346377151758</v>
+        <v>328.7333725360964</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24994,28 +25159,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2429625538676195</v>
+        <v>-0.2437332104075056</v>
       </c>
       <c r="J11" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K11" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1942585544452761</v>
+        <v>0.1974596973747303</v>
       </c>
       <c r="M11" t="n">
-        <v>2.926351592590507</v>
+        <v>2.909972450084691</v>
       </c>
       <c r="N11" t="n">
-        <v>13.65578924683792</v>
+        <v>13.56332793053252</v>
       </c>
       <c r="O11" t="n">
-        <v>3.695374033415011</v>
+        <v>3.682842371122137</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3367355476469</v>
+        <v>327.3450841355926</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25076,28 +25241,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2280115234102838</v>
+        <v>-0.2266649650266722</v>
       </c>
       <c r="J12" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2557264744034518</v>
+        <v>0.25600449699859</v>
       </c>
       <c r="M12" t="n">
-        <v>2.286796539322105</v>
+        <v>2.277058480227991</v>
       </c>
       <c r="N12" t="n">
-        <v>8.439039881000877</v>
+        <v>8.387643655440225</v>
       </c>
       <c r="O12" t="n">
-        <v>2.905002561272688</v>
+        <v>2.896142892786926</v>
       </c>
       <c r="P12" t="n">
-        <v>332.20456203713</v>
+        <v>332.1899699462391</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25139,7 +25304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M429"/>
+  <dimension ref="A1:M432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53857,6 +54022,207 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-42.82760645569636,173.3351138873687</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-42.82802935252568,173.33441993088758</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-42.82851601310967,173.33380174484327</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-42.82906464995877,173.3332702830351</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-42.82959014638799,173.33271683769405</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-42.83011112830233,173.33216235198537</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-42.83065271368336,173.33162698943542</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-42.83119606842281,173.3310893358777</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-42.83175219294092,173.33060019623437</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-42.83231872568464,173.33014091193445</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-42.83292404319457,173.32977719861674</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-42.82759902984992,173.33510373266907</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-42.82802053031544,173.3344078667437</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-42.82850738217868,173.3337894278665</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-42.82906197600314,173.3332661461227</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-42.82958875970508,173.33271458541017</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-42.83010902192644,173.33215884441117</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-42.83064585710771,173.33161334984268</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-42.83119222668633,173.33108005890267</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-42.8317500621124,173.33059494631863</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-42.8323172906273,173.3301373762517</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-42.83292356483994,173.32977602004598</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-42.82759598334855,173.33509956663917</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-42.82801488156142,173.3344001422217</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-42.82850160752626,173.33378118701344</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-42.829056865776366,173.3332582400244</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-42.829586968572926,173.33271167621032</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-42.830108395706574,173.33215780161893</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-42.830642200266695,173.3316060753945</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-42.83118953305456,173.33107355435766</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-42.83174945330421,173.33059344634273</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-42.832320073768706,173.33014423333353</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-42.83292582615265,173.3297815914716</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M432"/>
+  <dimension ref="A1:M434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19874,6 +19874,96 @@
         <v>327.44</v>
       </c>
       <c r="M432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>316.81</v>
+      </c>
+      <c r="C433" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="D433" t="n">
+        <v>313</v>
+      </c>
+      <c r="E433" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="F433" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="G433" t="n">
+        <v>330.7</v>
+      </c>
+      <c r="H433" t="n">
+        <v>332.27</v>
+      </c>
+      <c r="I433" t="n">
+        <v>325.01</v>
+      </c>
+      <c r="J433" t="n">
+        <v>322.06</v>
+      </c>
+      <c r="K433" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="L433" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>314.61</v>
+      </c>
+      <c r="C434" t="n">
+        <v>308.51</v>
+      </c>
+      <c r="D434" t="n">
+        <v>312.25</v>
+      </c>
+      <c r="E434" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="F434" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="G434" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="H434" t="n">
+        <v>331.87</v>
+      </c>
+      <c r="I434" t="n">
+        <v>324.66</v>
+      </c>
+      <c r="J434" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="K434" t="n">
+        <v>320.11</v>
+      </c>
+      <c r="L434" t="n">
+        <v>326.84</v>
+      </c>
+      <c r="M434" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19890,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24253,6 +24343,26 @@
       </c>
       <c r="B436" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -24421,28 +24531,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5028685121312754</v>
+        <v>-0.4996131566172111</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1750693358066119</v>
+        <v>0.1743882962285301</v>
       </c>
       <c r="M2" t="n">
-        <v>6.827234826572838</v>
+        <v>6.811423490010752</v>
       </c>
       <c r="N2" t="n">
-        <v>67.4987327119279</v>
+        <v>67.2570123144603</v>
       </c>
       <c r="O2" t="n">
-        <v>8.215761237519498</v>
+        <v>8.201037270642068</v>
       </c>
       <c r="P2" t="n">
-        <v>325.4232414949274</v>
+        <v>325.3880915778105</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24503,28 +24613,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4436312190203279</v>
+        <v>-0.4414377073593204</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1895389578483997</v>
+        <v>0.1893424379347531</v>
       </c>
       <c r="M3" t="n">
-        <v>5.566685150003532</v>
+        <v>5.551999855698103</v>
       </c>
       <c r="N3" t="n">
-        <v>47.67132544186317</v>
+        <v>47.48316519546172</v>
       </c>
       <c r="O3" t="n">
-        <v>6.90444244250491</v>
+        <v>6.890802942724579</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6376586850571</v>
+        <v>318.6139742504015</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24585,28 +24695,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.48893723010281</v>
+        <v>-0.4877515077898551</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2957963282118395</v>
+        <v>0.2966647256660329</v>
       </c>
       <c r="M4" t="n">
-        <v>4.523480509193356</v>
+        <v>4.508882072411799</v>
       </c>
       <c r="N4" t="n">
-        <v>32.23970750101076</v>
+        <v>32.10000219479174</v>
       </c>
       <c r="O4" t="n">
-        <v>5.67800206947926</v>
+        <v>5.665686383377723</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3570611593308</v>
+        <v>324.34425813025</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24667,28 +24777,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4669053100740676</v>
+        <v>-0.4659079693790988</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4443259985736029</v>
+        <v>0.4454580522951472</v>
       </c>
       <c r="M5" t="n">
-        <v>3.102610714900799</v>
+        <v>3.094036075622795</v>
       </c>
       <c r="N5" t="n">
-        <v>15.44384197557499</v>
+        <v>15.37939318524089</v>
       </c>
       <c r="O5" t="n">
-        <v>3.929865388989169</v>
+        <v>3.921656943849231</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9855939916233</v>
+        <v>334.9748255582342</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24749,28 +24859,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4616730051087464</v>
+        <v>-0.4604546486133058</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5977318559870632</v>
+        <v>0.5984391435806747</v>
       </c>
       <c r="M6" t="n">
-        <v>2.196280069015198</v>
+        <v>2.191981503475241</v>
       </c>
       <c r="N6" t="n">
-        <v>8.057988850173162</v>
+        <v>8.029632438846702</v>
       </c>
       <c r="O6" t="n">
-        <v>2.838659692561467</v>
+        <v>2.833660607561657</v>
       </c>
       <c r="P6" t="n">
-        <v>338.7848746035284</v>
+        <v>338.7716408749728</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24831,28 +24941,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4074511558215141</v>
+        <v>-0.4079654660820807</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5356010254899818</v>
+        <v>0.5384963404056005</v>
       </c>
       <c r="M7" t="n">
-        <v>2.087730342367425</v>
+        <v>2.081231555601959</v>
       </c>
       <c r="N7" t="n">
-        <v>8.08629200815354</v>
+        <v>8.050628009891032</v>
       </c>
       <c r="O7" t="n">
-        <v>2.843640625703878</v>
+        <v>2.837362861865051</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0089568841316</v>
+        <v>342.0145443862614</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24913,28 +25023,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3325821965354217</v>
+        <v>-0.3341222119738933</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4576067646733546</v>
+        <v>0.4617334875942363</v>
       </c>
       <c r="M8" t="n">
-        <v>2.035422010939206</v>
+        <v>2.033891809819321</v>
       </c>
       <c r="N8" t="n">
-        <v>7.364924226314887</v>
+        <v>7.345261249804374</v>
       </c>
       <c r="O8" t="n">
-        <v>2.713839388452251</v>
+        <v>2.710214244262688</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7485239522255</v>
+        <v>342.7652528751523</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24995,28 +25105,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2995221164852747</v>
+        <v>-0.3008286909748045</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K9" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3865477330707593</v>
+        <v>0.3905254756347465</v>
       </c>
       <c r="M9" t="n">
-        <v>2.172280500424717</v>
+        <v>2.168753166208836</v>
       </c>
       <c r="N9" t="n">
-        <v>7.998045982689492</v>
+        <v>7.971412032828932</v>
       </c>
       <c r="O9" t="n">
-        <v>2.828081678928226</v>
+        <v>2.823368915467642</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3601112231614</v>
+        <v>334.3743043308173</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25077,28 +25187,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.253631045656875</v>
+        <v>-0.2533606568223429</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K10" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2550931616363068</v>
+        <v>0.2564545440939213</v>
       </c>
       <c r="M10" t="n">
-        <v>2.51146820047339</v>
+        <v>2.500964170342246</v>
       </c>
       <c r="N10" t="n">
-        <v>10.55252595380516</v>
+        <v>10.50427397412945</v>
       </c>
       <c r="O10" t="n">
-        <v>3.248465168938273</v>
+        <v>3.241029770633008</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7333725360964</v>
+        <v>328.7304346159307</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25159,28 +25269,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2437332104075056</v>
+        <v>-0.2442769258603317</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K11" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1974596973747303</v>
+        <v>0.1996341919432715</v>
       </c>
       <c r="M11" t="n">
-        <v>2.909972450084691</v>
+        <v>2.899318429683939</v>
       </c>
       <c r="N11" t="n">
-        <v>13.56332793053252</v>
+        <v>13.50234049677969</v>
       </c>
       <c r="O11" t="n">
-        <v>3.682842371122137</v>
+        <v>3.674553101641028</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3450841355926</v>
+        <v>327.3509904693531</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25241,28 +25351,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2266649650266722</v>
+        <v>-0.226102834252038</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K12" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25600449699859</v>
+        <v>0.2567948151774698</v>
       </c>
       <c r="M12" t="n">
-        <v>2.277058480227991</v>
+        <v>2.269085127207123</v>
       </c>
       <c r="N12" t="n">
-        <v>8.387643655440225</v>
+        <v>8.350741796382696</v>
       </c>
       <c r="O12" t="n">
-        <v>2.896142892786926</v>
+        <v>2.889765007121288</v>
       </c>
       <c r="P12" t="n">
-        <v>332.1899699462391</v>
+        <v>332.1838635704728</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25304,7 +25414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M432"/>
+  <dimension ref="A1:M434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54223,6 +54333,140 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-42.827587097718684,173.33508741572095</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-42.828010121375065,173.3343936327942</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-42.82849918589764,173.33377773117226</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-42.82905864841368,173.3332609979655</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-42.82958615967451,173.33271036237818</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-42.83010981893355,173.33216017160137</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-42.8306393560567,173.3316004174909</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-42.83118617705378,173.33106545033513</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-42.83175067092058,173.33059644629452</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-42.83231876917122,173.33014101907634</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-42.83292252115703,173.3297734486189</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-42.82757313458338,173.3350683214279</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-42.828000283655385,173.33438017998043</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-42.828494528919244,173.33377108532468</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-42.82905353818655,173.33325309186807</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-42.829585292997606,173.33270895470093</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-42.830107541770374,173.33215637962948</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-42.83063732447795,173.3315963761315</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-42.83118463152691,173.33106171821981</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-42.83175227991351,173.33060041051667</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-42.83231807338587,173.3301393048059</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-42.832923216945645,173.32977516290362</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M434"/>
+  <dimension ref="A1:M435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19964,6 +19964,51 @@
         <v>326.84</v>
       </c>
       <c r="M434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>313.89</v>
+      </c>
+      <c r="C435" t="n">
+        <v>306.27</v>
+      </c>
+      <c r="D435" t="n">
+        <v>311.24</v>
+      </c>
+      <c r="E435" t="n">
+        <v>322.18</v>
+      </c>
+      <c r="F435" t="n">
+        <v>327.37</v>
+      </c>
+      <c r="G435" t="n">
+        <v>331.44</v>
+      </c>
+      <c r="H435" t="n">
+        <v>332.24</v>
+      </c>
+      <c r="I435" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="J435" t="n">
+        <v>321.69</v>
+      </c>
+      <c r="K435" t="n">
+        <v>318.66</v>
+      </c>
+      <c r="L435" t="n">
+        <v>325.56</v>
+      </c>
+      <c r="M435" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19980,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24363,6 +24408,16 @@
       </c>
       <c r="B438" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -24531,28 +24586,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4996131566172111</v>
+        <v>-0.4987741478717231</v>
       </c>
       <c r="J2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1743882962285301</v>
+        <v>0.1745591104178572</v>
       </c>
       <c r="M2" t="n">
-        <v>6.811423490010752</v>
+        <v>6.799747687730711</v>
       </c>
       <c r="N2" t="n">
-        <v>67.2570123144603</v>
+        <v>67.11061195230181</v>
       </c>
       <c r="O2" t="n">
-        <v>8.201037270642068</v>
+        <v>8.192106685847165</v>
       </c>
       <c r="P2" t="n">
-        <v>325.3880915778105</v>
+        <v>325.3789899508306</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24613,28 +24668,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4414377073593204</v>
+        <v>-0.4416398357250605</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1893424379347531</v>
+        <v>0.1902004331754417</v>
       </c>
       <c r="M3" t="n">
-        <v>5.551999855698103</v>
+        <v>5.540336201368541</v>
       </c>
       <c r="N3" t="n">
-        <v>47.48316519546172</v>
+        <v>47.37425436012761</v>
       </c>
       <c r="O3" t="n">
-        <v>6.890802942724579</v>
+        <v>6.882895783035481</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6139742504015</v>
+        <v>318.6161669533942</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24695,28 +24750,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4877515077898551</v>
+        <v>-0.4877451688508728</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2966647256660329</v>
+        <v>0.2976356972820374</v>
       </c>
       <c r="M4" t="n">
-        <v>4.508882072411799</v>
+        <v>4.498526339157233</v>
       </c>
       <c r="N4" t="n">
-        <v>32.10000219479174</v>
+        <v>32.02603954527149</v>
       </c>
       <c r="O4" t="n">
-        <v>5.665686383377723</v>
+        <v>5.659155373840826</v>
       </c>
       <c r="P4" t="n">
-        <v>324.34425813025</v>
+        <v>324.3441893649858</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24777,28 +24832,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4659079693790988</v>
+        <v>-0.4660214014406466</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4454580522951472</v>
+        <v>0.4467310221974156</v>
       </c>
       <c r="M5" t="n">
-        <v>3.094036075622795</v>
+        <v>3.087457192259988</v>
       </c>
       <c r="N5" t="n">
-        <v>15.37939318524089</v>
+        <v>15.34411343622194</v>
       </c>
       <c r="O5" t="n">
-        <v>3.921656943849231</v>
+        <v>3.917156294586921</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9748255582342</v>
+        <v>334.9760560773644</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24859,28 +24914,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4604546486133058</v>
+        <v>-0.4600242177100556</v>
       </c>
       <c r="J6" t="n">
+        <v>434</v>
+      </c>
+      <c r="K6" t="n">
         <v>433</v>
       </c>
-      <c r="K6" t="n">
-        <v>432</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.5984391435806747</v>
+        <v>0.5990502711029031</v>
       </c>
       <c r="M6" t="n">
-        <v>2.191981503475241</v>
+        <v>2.188966408840743</v>
       </c>
       <c r="N6" t="n">
-        <v>8.029632438846702</v>
+        <v>8.013316807178395</v>
       </c>
       <c r="O6" t="n">
-        <v>2.833660607561657</v>
+        <v>2.830780247065885</v>
       </c>
       <c r="P6" t="n">
-        <v>338.7716408749728</v>
+        <v>338.7669444136015</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24941,28 +24996,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4079654660820807</v>
+        <v>-0.40779311331325</v>
       </c>
       <c r="J7" t="n">
+        <v>434</v>
+      </c>
+      <c r="K7" t="n">
         <v>433</v>
       </c>
-      <c r="K7" t="n">
-        <v>432</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5384963404056005</v>
+        <v>0.5394412476989012</v>
       </c>
       <c r="M7" t="n">
-        <v>2.081231555601959</v>
+        <v>2.077185658799702</v>
       </c>
       <c r="N7" t="n">
-        <v>8.050628009891032</v>
+        <v>8.032392651798576</v>
       </c>
       <c r="O7" t="n">
-        <v>2.837362861865051</v>
+        <v>2.834147605859401</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0145443862614</v>
+        <v>342.0126638332739</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -25023,28 +25078,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3341222119738933</v>
+        <v>-0.3347923939322257</v>
       </c>
       <c r="J8" t="n">
+        <v>434</v>
+      </c>
+      <c r="K8" t="n">
         <v>433</v>
       </c>
-      <c r="K8" t="n">
-        <v>432</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.4617334875942363</v>
+        <v>0.4637131599939192</v>
       </c>
       <c r="M8" t="n">
-        <v>2.033891809819321</v>
+        <v>2.032611125186771</v>
       </c>
       <c r="N8" t="n">
-        <v>7.345261249804374</v>
+        <v>7.333700184811564</v>
       </c>
       <c r="O8" t="n">
-        <v>2.710214244262688</v>
+        <v>2.708080535141369</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7652528751523</v>
+        <v>342.7725652768763</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -25105,28 +25160,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3008286909748045</v>
+        <v>-0.3012563330269162</v>
       </c>
       <c r="J9" t="n">
+        <v>434</v>
+      </c>
+      <c r="K9" t="n">
         <v>433</v>
       </c>
-      <c r="K9" t="n">
-        <v>432</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3905254756347465</v>
+        <v>0.3922540823651433</v>
       </c>
       <c r="M9" t="n">
-        <v>2.168753166208836</v>
+        <v>2.165885887853489</v>
       </c>
       <c r="N9" t="n">
-        <v>7.971412032828932</v>
+        <v>7.955202074399177</v>
       </c>
       <c r="O9" t="n">
-        <v>2.823368915467642</v>
+        <v>2.820496777945186</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3743043308173</v>
+        <v>334.3789703628408</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25187,28 +25242,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2533606568223429</v>
+        <v>-0.2534604778525895</v>
       </c>
       <c r="J10" t="n">
+        <v>434</v>
+      </c>
+      <c r="K10" t="n">
         <v>433</v>
       </c>
-      <c r="K10" t="n">
-        <v>432</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2564545440939213</v>
+        <v>0.2574987375141835</v>
       </c>
       <c r="M10" t="n">
-        <v>2.500964170342246</v>
+        <v>2.495827147287826</v>
       </c>
       <c r="N10" t="n">
-        <v>10.50427397412945</v>
+        <v>10.48013453705476</v>
       </c>
       <c r="O10" t="n">
-        <v>3.241029770633008</v>
+        <v>3.237303590498544</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7304346159307</v>
+        <v>328.7315237700993</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25269,28 +25324,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2442769258603317</v>
+        <v>-0.2452009571728852</v>
       </c>
       <c r="J11" t="n">
+        <v>434</v>
+      </c>
+      <c r="K11" t="n">
         <v>433</v>
       </c>
-      <c r="K11" t="n">
-        <v>432</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1996341919432715</v>
+        <v>0.2014750202816762</v>
       </c>
       <c r="M11" t="n">
-        <v>2.899318429683939</v>
+        <v>2.897353871594926</v>
       </c>
       <c r="N11" t="n">
-        <v>13.50234049677969</v>
+        <v>13.48142771703919</v>
       </c>
       <c r="O11" t="n">
-        <v>3.674553101641028</v>
+        <v>3.671706376746266</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3509904693531</v>
+        <v>327.3610726389474</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25351,28 +25406,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.226102834252038</v>
+        <v>-0.2263377091897962</v>
       </c>
       <c r="J12" t="n">
+        <v>434</v>
+      </c>
+      <c r="K12" t="n">
         <v>433</v>
       </c>
-      <c r="K12" t="n">
-        <v>432</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2567948151774698</v>
+        <v>0.2580735333583116</v>
       </c>
       <c r="M12" t="n">
-        <v>2.269085127207123</v>
+        <v>2.265252249037163</v>
       </c>
       <c r="N12" t="n">
-        <v>8.350741796382696</v>
+        <v>8.332119593001817</v>
       </c>
       <c r="O12" t="n">
-        <v>2.889765007121288</v>
+        <v>2.88654111230064</v>
       </c>
       <c r="P12" t="n">
-        <v>332.1838635704728</v>
+        <v>332.186426307172</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25414,7 +25469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M434"/>
+  <dimension ref="A1:M435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54467,6 +54522,73 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-42.8275685648293,173.33506207238844</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-42.82798606656084,173.3343607385023</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-42.828488257521045,173.33376213558483</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-42.82904747721878,173.3332437148705</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-42.82958315519452,173.33270548243058</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-42.830114031685106,173.33216718675015</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-42.830639203688285,173.33160011438892</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-42.83118745763309,173.33106854265944</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-42.8317490619275,173.33059248207255</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-42.83231176782984,173.33012376923182</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-42.83291765063612,173.32976144862707</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
